--- a/daten/Zielliste_CH_Industrie.xlsx
+++ b/daten/Zielliste_CH_Industrie.xlsx
@@ -8533,7 +8533,7 @@
       </c>
       <c r="Y77" s="67" t="inlineStr">
         <is>
-          <t>https://jobs.baumer.com/</t>
+          <t>https://jobs.baumer.com/ — nicht abrufbar ohne Rendern, Prospective-Widget</t>
         </is>
       </c>
     </row>
